--- a/informes_data/Euroleague/2025-26/playoffs/aggregate_individual/AGG_IND_ZALGIRIS KAUNAS.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate_individual/AGG_IND_ZALGIRIS KAUNAS.xlsx
@@ -565,13 +565,13 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1816</v>
+        <v>5.2679</v>
       </c>
       <c r="E2" t="n">
-        <v>7.483499999999999</v>
+        <v>7.231999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.3018</v>
+        <v>-1.9641</v>
       </c>
       <c r="G2" t="n">
         <v>-2.1798</v>
@@ -610,13 +610,13 @@
         <v>8.8714</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2298</v>
+        <v>-0.1437</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0304</v>
+        <v>0.7788999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.2602</v>
+        <v>-0.9226</v>
       </c>
       <c r="V2" t="n">
         <v>3.042</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. WRIGHT</t>
+          <t>E. ULANOVAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7442</v>
+        <v>4.7459</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0074</v>
+        <v>8.4747</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7368</v>
+        <v>-3.7288</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.7483000000000009</v>
+        <v>-0.4624999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>2.989099999999999</v>
+        <v>0.5606</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.7374</v>
+        <v>-1.0231</v>
       </c>
       <c r="J3" t="n">
-        <v>4.714499999999999</v>
+        <v>5.4023</v>
       </c>
       <c r="K3" t="n">
-        <v>5.3315</v>
+        <v>3.7056</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.617</v>
+        <v>1.6967</v>
       </c>
       <c r="M3" t="n">
-        <v>-5.4628</v>
+        <v>-5.8648</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.3423</v>
+        <v>-3.145</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.1205</v>
+        <v>-2.7199</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.9572</v>
+        <v>3.6395</v>
       </c>
       <c r="Q3" t="n">
-        <v>-9.7813</v>
+        <v>-1.8198</v>
       </c>
       <c r="R3" t="n">
-        <v>6.8243</v>
+        <v>5.4594</v>
       </c>
       <c r="S3" t="n">
-        <v>2.9308</v>
+        <v>0.3204</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4671</v>
+        <v>1.1469</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4637000000000001</v>
+        <v>-0.8266</v>
       </c>
       <c r="V3" t="n">
-        <v>4.5188</v>
+        <v>1.2485</v>
       </c>
       <c r="W3" t="n">
-        <v>4.6071</v>
+        <v>3.7455</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.0882</v>
+        <v>-2.4969</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. ULANOVAS</t>
+          <t>M. WRIGHT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7089</v>
+        <v>2.25</v>
       </c>
       <c r="E4" t="n">
-        <v>7.1368</v>
+        <v>0.8219999999999996</v>
       </c>
       <c r="F4" t="n">
-        <v>-4.428100000000001</v>
+        <v>1.428</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4624999999999999</v>
+        <v>-0.7483000000000009</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5606</v>
+        <v>2.989099999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.0231</v>
+        <v>-3.7374</v>
       </c>
       <c r="J4" t="n">
-        <v>5.4023</v>
+        <v>4.714499999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>3.7056</v>
+        <v>5.3315</v>
       </c>
       <c r="L4" t="n">
-        <v>1.6967</v>
+        <v>-0.617</v>
       </c>
       <c r="M4" t="n">
-        <v>-5.8648</v>
+        <v>-5.4628</v>
       </c>
       <c r="N4" t="n">
-        <v>-3.145</v>
+        <v>-2.3423</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.7199</v>
+        <v>-3.1205</v>
       </c>
       <c r="P4" t="n">
-        <v>3.6395</v>
+        <v>-2.9572</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.8198</v>
+        <v>-9.7813</v>
       </c>
       <c r="R4" t="n">
-        <v>5.4594</v>
+        <v>6.8243</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.7167</v>
+        <v>1.4366</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1909999999999999</v>
+        <v>1.2818</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.5257</v>
+        <v>0.1549</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2485</v>
+        <v>4.5188</v>
       </c>
       <c r="W4" t="n">
-        <v>3.7455</v>
+        <v>4.6071</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.4969</v>
+        <v>-0.0882</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8874000000000002</v>
+        <v>-0.09860000000000013</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01900000000000013</v>
+        <v>-1.0315</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8682000000000001</v>
+        <v>0.9329999999999999</v>
       </c>
       <c r="G5" t="n">
         <v>-4.6074</v>
@@ -844,13 +844,13 @@
         <v>5.6869</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8333999999999999</v>
+        <v>-0.1527</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1019</v>
+        <v>0.05130000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2685999999999999</v>
+        <v>-0.204</v>
       </c>
       <c r="V5" t="n">
         <v>1.4768</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. BIRUTIS</t>
+          <t>N. WILLIAMS-GOSS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1691999999999999</v>
+        <v>-0.7027000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>3.15</v>
+        <v>3.6926</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.3191</v>
+        <v>-4.3954</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8659</v>
+        <v>0.1410999999999998</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0685</v>
+        <v>1.7057</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.9346</v>
+        <v>-1.5646</v>
       </c>
       <c r="J6" t="n">
-        <v>1.816</v>
+        <v>7.012199999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>1.7043</v>
+        <v>5.117000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1118</v>
+        <v>1.8952</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.6821</v>
+        <v>-6.8711</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6356999999999999</v>
+        <v>-3.4112</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.0463</v>
+        <v>-3.4598</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3649</v>
+        <v>-1.3648</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2275</v>
+        <v>-8.871400000000001</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5923</v>
+        <v>7.506600000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>1.899</v>
+        <v>-1.5893</v>
       </c>
       <c r="T6" t="n">
-        <v>2.3349</v>
+        <v>0.1713</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4359</v>
+        <v>-1.7606</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.5669</v>
+        <v>2.1102</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.7734</v>
+        <v>5.3807</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.7935</v>
+        <v>-3.2703</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3743</v>
+        <v>-1.5359</v>
       </c>
       <c r="E7" t="n">
         <v>-1.954</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5797</v>
+        <v>0.418</v>
       </c>
       <c r="G7" t="n">
         <v>-2.0927</v>
@@ -1000,13 +1000,13 @@
         <v>0.455</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4909000000000001</v>
+        <v>0.3293</v>
       </c>
       <c r="T7" t="n">
         <v>0.3593</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1316</v>
+        <v>-0.0301</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. GIEDRAITIS</t>
+          <t>L. BIRUTIS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.0524</v>
+        <v>-1.6279</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3348</v>
+        <v>1.6325</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.7175</v>
+        <v>-3.2604</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.1473</v>
+        <v>-0.8659</v>
       </c>
       <c r="H8" t="n">
-        <v>0.761</v>
+        <v>1.0685</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.9083</v>
+        <v>-1.9346</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.07779999999999998</v>
+        <v>1.816</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8453999999999999</v>
+        <v>1.7043</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.9231</v>
+        <v>0.1118</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.0695</v>
+        <v>-2.6821</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.08439999999999998</v>
+        <v>-0.6356999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.9852</v>
+        <v>-2.0463</v>
       </c>
       <c r="P8" t="n">
+        <v>1.3649</v>
+      </c>
+      <c r="Q8" t="n">
         <v>-0.2275</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-1.1374</v>
-      </c>
       <c r="R8" t="n">
-        <v>0.9099</v>
+        <v>1.5923</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6776</v>
+        <v>0.44</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1196</v>
+        <v>0.8172999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5579000000000001</v>
+        <v>-0.3773</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-2.5669</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.7734</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.7935</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. WILLIAMS-GOSS</t>
+          <t>D. GIEDRAITIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.639</v>
+        <v>-2.8387</v>
       </c>
       <c r="E9" t="n">
-        <v>2.193</v>
+        <v>-1.2181</v>
       </c>
       <c r="F9" t="n">
-        <v>-5.832</v>
+        <v>-1.6206</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1410999999999998</v>
+        <v>-2.1473</v>
       </c>
       <c r="H9" t="n">
-        <v>1.7057</v>
+        <v>0.761</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.5646</v>
+        <v>-2.9083</v>
       </c>
       <c r="J9" t="n">
-        <v>7.012199999999999</v>
+        <v>-0.07779999999999998</v>
       </c>
       <c r="K9" t="n">
-        <v>5.117000000000001</v>
+        <v>0.8453999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>1.8952</v>
+        <v>-0.9231</v>
       </c>
       <c r="M9" t="n">
-        <v>-6.8711</v>
+        <v>-2.0695</v>
       </c>
       <c r="N9" t="n">
-        <v>-3.4112</v>
+        <v>-0.08439999999999998</v>
       </c>
       <c r="O9" t="n">
-        <v>-3.4598</v>
+        <v>-1.9852</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.3648</v>
+        <v>-0.2275</v>
       </c>
       <c r="Q9" t="n">
-        <v>-8.871400000000001</v>
+        <v>-1.1374</v>
       </c>
       <c r="R9" t="n">
-        <v>7.506600000000001</v>
+        <v>0.9099</v>
       </c>
       <c r="S9" t="n">
-        <v>-4.5255</v>
+        <v>-0.4639</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.3283</v>
+        <v>-0.0029</v>
       </c>
       <c r="U9" t="n">
-        <v>-3.1972</v>
+        <v>-0.461</v>
       </c>
       <c r="V9" t="n">
-        <v>2.1102</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>5.3807</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.2703</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.525700000000001</v>
+        <v>-3.7226</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.8939</v>
+        <v>-2.8165</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6317</v>
+        <v>-0.9062000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>-5.8544</v>
@@ -1234,13 +1234,13 @@
         <v>4.5494</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6712</v>
+        <v>0.1317</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3589</v>
+        <v>0.7188</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.3124</v>
+        <v>-0.5869</v>
       </c>
       <c r="V10" t="n">
         <v>1.0901</v>
@@ -1267,13 +1267,13 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.6444</v>
+        <v>-4.9813</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8308</v>
+        <v>-0.2145000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.8135</v>
+        <v>-4.7668</v>
       </c>
       <c r="G11" t="n">
         <v>-6.7205</v>
@@ -1312,13 +1312,13 @@
         <v>9.3264</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.531</v>
+        <v>-0.8678999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5737999999999999</v>
+        <v>1.0424</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.9571</v>
+        <v>-1.9103</v>
       </c>
       <c r="V11" t="n">
         <v>3.5169</v>
@@ -1345,13 +1345,13 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.26</v>
+        <v>-6.8709</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.5284</v>
+        <v>-4.295</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.7316</v>
+        <v>-2.576</v>
       </c>
       <c r="G12" t="n">
         <v>-3.393</v>
@@ -1390,13 +1390,13 @@
         <v>0.2275</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6824</v>
+        <v>-0.2933</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2155</v>
+        <v>0.018</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4669</v>
+        <v>-0.3113</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.2902</v>
+        <v>-7.7685</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.8488</v>
+        <v>-2.2887</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.4415</v>
+        <v>-5.4798</v>
       </c>
       <c r="G13" t="n">
         <v>-4.861000000000001</v>
@@ -1468,13 +1468,13 @@
         <v>4.3219</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7039</v>
+        <v>-1.1822</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6646</v>
+        <v>1.2246</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.3685</v>
+        <v>-2.4067</v>
       </c>
       <c r="V13" t="n">
         <v>-2.1802</v>
@@ -1501,13 +1501,13 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>-22.4331</v>
+        <v>-17.8833</v>
       </c>
       <c r="E14" t="n">
-        <v>6.598999999999998</v>
+        <v>8.035499999999995</v>
       </c>
       <c r="F14" t="n">
-        <v>-29.0321</v>
+        <v>-25.9191</v>
       </c>
       <c r="G14" t="n">
         <v>-33.79170000000001</v>
@@ -1525,7 +1525,7 @@
         <v>19.7286</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6258000000000012</v>
+        <v>-0.625800000000001</v>
       </c>
       <c r="M14" t="n">
         <v>-52.8944</v>
@@ -1534,7 +1534,7 @@
         <v>-22.8886</v>
       </c>
       <c r="O14" t="n">
-        <v>-30.0056</v>
+        <v>-30.00559999999999</v>
       </c>
       <c r="P14" t="n">
         <v>5.686500000000001</v>
@@ -1546,13 +1546,13 @@
         <v>55.73099999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>-6.584000000000001</v>
+        <v>-2.035</v>
       </c>
       <c r="T14" t="n">
-        <v>6.171100000000002</v>
+        <v>7.607699999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-12.7551</v>
+        <v>-9.642500000000002</v>
       </c>
       <c r="V14" t="n">
         <v>12.2562</v>
